--- a/mlef_pipeline/results/OS_6/IO_ONLY/RWD_PYRAD/rwd-only/results.xlsx
+++ b/mlef_pipeline/results/OS_6/IO_ONLY/RWD_PYRAD/rwd-only/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.63 ± 0.06</t>
+          <t>0.65 ± 0.05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.57 ± 0.04</t>
+          <t>0.61 ± 0.05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.55 ± 0.13</t>
+          <t>0.59 ± 0.08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.66 ± 0.20</t>
+          <t>0.68 ± 0.06</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,22 +498,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.70 ± 0.11</t>
+          <t>0.64 ± 0.12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -533,17 +533,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="F4" t="n">
